--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18852" windowHeight="6744"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="30468" windowHeight="12840"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -19,51 +19,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
-  <x:si>
-    <x:t>몬스터 세계에 접속했습니다...</x:t>
-  </x:si>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <x:si>
     <x:t>두둥..지금.. 배가 고픕니다!</x:t>
   </x:si>
   <x:si>
+    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>다만 아직 야근이 남아 있습니다. 좀 더 고생해주세요.</x:t>
   </x:si>
   <x:si>
-    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+    <x:t>dialogue_group_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용사님이시어..고생하셨군요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용사님이시어..고생하셨군요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
+    <x:t>dialogue_mainstream_1_1_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
   </x:si>
   <x:si>
     <x:t>고유 ID</x:t>
@@ -72,25 +84,16 @@
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
     <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 세계에 접속했습니다...&lt;np&gt;이 세계에서 빠져나가고 싶다면&lt;np&gt;몬스터를 물리치세요..</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -216,7 +219,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -225,7 +228,7 @@
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -240,16 +243,16 @@
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -856,70 +859,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:P35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
-    <x:col min="3" max="5" width="50.7265625" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="84.22265625" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="32" style="1" customWidth="1"/>
+    <x:col min="5" max="6" width="50.7265625" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="F3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="6"/>
       <x:c r="C4" s="5" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D4" s="5"/>
+      <x:c r="E4" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="5"/>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="4"/>
@@ -929,18 +941,19 @@
       <x:c r="M4" s="4"/>
       <x:c r="N4" s="4"/>
       <x:c r="O4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="6"/>
       <x:c r="C5" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5"/>
-      <x:c r="F5" s="4"/>
+      <x:c r="F5" s="5"/>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="4"/>
@@ -950,20 +963,21 @@
       <x:c r="M5" s="4"/>
       <x:c r="N5" s="4"/>
       <x:c r="O5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P5" s="4"/>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="6"/>
       <x:c r="C6" s="5" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5" t="s">
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="4"/>
@@ -973,18 +987,19 @@
       <x:c r="M6" s="4"/>
       <x:c r="N6" s="4"/>
       <x:c r="O6" s="4"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P6" s="4"/>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="5"/>
       <x:c r="C7" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="5"/>
       <x:c r="E7" s="5"/>
-      <x:c r="F7" s="4"/>
+      <x:c r="F7" s="5"/>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
@@ -994,18 +1009,19 @@
       <x:c r="M7" s="4"/>
       <x:c r="N7" s="4"/>
       <x:c r="O7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="4"/>
+    </x:row>
+    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
-      <x:c r="F8" s="4"/>
+      <x:c r="F8" s="7"/>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
@@ -1015,20 +1031,21 @@
       <x:c r="M8" s="4"/>
       <x:c r="N8" s="4"/>
       <x:c r="O8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P8" s="4"/>
+    </x:row>
+    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
-      <x:c r="E9" s="5" t="s">
+      <x:c r="E9" s="7"/>
+      <x:c r="F9" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F9" s="4"/>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
@@ -1038,10 +1055,11 @@
       <x:c r="M9" s="4"/>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="4"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="4"/>
+    </x:row>
+    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="8"/>
       <x:c r="C10" s="8" t="s">
@@ -1049,7 +1067,7 @@
       </x:c>
       <x:c r="D10" s="8"/>
       <x:c r="E10" s="8"/>
-      <x:c r="F10" s="4"/>
+      <x:c r="F10" s="8"/>
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
@@ -1059,14 +1077,15 @@
       <x:c r="M10" s="4"/>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="4"/>
+    </x:row>
+    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="8"/>
       <x:c r="B11" s="8"/>
       <x:c r="C11" s="8"/>
       <x:c r="D11" s="8"/>
       <x:c r="E11" s="8"/>
-      <x:c r="F11" s="4"/>
+      <x:c r="F11" s="8"/>
       <x:c r="G11" s="4"/>
       <x:c r="H11" s="4"/>
       <x:c r="I11" s="4"/>
@@ -1076,14 +1095,15 @@
       <x:c r="M11" s="4"/>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="7"/>
       <x:c r="B12" s="7"/>
       <x:c r="C12" s="7"/>
       <x:c r="D12" s="7"/>
       <x:c r="E12" s="7"/>
-      <x:c r="F12" s="4"/>
+      <x:c r="F12" s="7"/>
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="4"/>
@@ -1093,14 +1113,15 @@
       <x:c r="M12" s="4"/>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="5"/>
       <x:c r="B13" s="5"/>
       <x:c r="C13" s="5"/>
       <x:c r="D13" s="5"/>
       <x:c r="E13" s="5"/>
-      <x:c r="F13" s="4"/>
+      <x:c r="F13" s="5"/>
       <x:c r="G13" s="4"/>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="4"/>
@@ -1110,14 +1131,15 @@
       <x:c r="M13" s="4"/>
       <x:c r="N13" s="4"/>
       <x:c r="O13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="8"/>
       <x:c r="B14" s="8"/>
       <x:c r="C14" s="8"/>
       <x:c r="D14" s="8"/>
       <x:c r="E14" s="8"/>
-      <x:c r="F14" s="4"/>
+      <x:c r="F14" s="8"/>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="4"/>
       <x:c r="I14" s="4"/>
@@ -1127,14 +1149,15 @@
       <x:c r="M14" s="4"/>
       <x:c r="N14" s="4"/>
       <x:c r="O14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="8"/>
       <x:c r="B15" s="8"/>
       <x:c r="C15" s="8"/>
       <x:c r="D15" s="8"/>
       <x:c r="E15" s="8"/>
-      <x:c r="F15" s="4"/>
+      <x:c r="F15" s="8"/>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="4"/>
       <x:c r="I15" s="4"/>
@@ -1144,146 +1167,167 @@
       <x:c r="M15" s="4"/>
       <x:c r="N15" s="4"/>
       <x:c r="O15" s="4"/>
-    </x:row>
-    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="P15" s="4"/>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="9"/>
       <x:c r="C16" s="9"/>
       <x:c r="D16" s="9"/>
       <x:c r="E16" s="9"/>
-    </x:row>
-    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F16" s="9"/>
+    </x:row>
+    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="10"/>
       <x:c r="B17" s="10"/>
       <x:c r="C17" s="10"/>
-      <x:c r="D17" s="10"/>
+      <x:c r="D17" s="9"/>
       <x:c r="E17" s="10"/>
-    </x:row>
-    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F17" s="10"/>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="10"/>
       <x:c r="B18" s="10"/>
       <x:c r="C18" s="10"/>
-      <x:c r="D18" s="10"/>
+      <x:c r="D18" s="9"/>
       <x:c r="E18" s="10"/>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F18" s="10"/>
+    </x:row>
+    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="10"/>
       <x:c r="B19" s="10"/>
       <x:c r="C19" s="10"/>
-      <x:c r="D19" s="10"/>
+      <x:c r="D19" s="9"/>
       <x:c r="E19" s="10"/>
-    </x:row>
-    <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F19" s="10"/>
+    </x:row>
+    <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="10"/>
       <x:c r="B20" s="10"/>
       <x:c r="C20" s="10"/>
-      <x:c r="D20" s="10"/>
+      <x:c r="D20" s="9"/>
       <x:c r="E20" s="10"/>
-    </x:row>
-    <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F20" s="10"/>
+    </x:row>
+    <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A21" s="10"/>
       <x:c r="B21" s="10"/>
       <x:c r="C21" s="10"/>
-      <x:c r="D21" s="10"/>
+      <x:c r="D21" s="9"/>
       <x:c r="E21" s="10"/>
-    </x:row>
-    <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F21" s="10"/>
+    </x:row>
+    <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A22" s="10"/>
       <x:c r="B22" s="10"/>
       <x:c r="C22" s="10"/>
-      <x:c r="D22" s="10"/>
+      <x:c r="D22" s="9"/>
       <x:c r="E22" s="10"/>
-    </x:row>
-    <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F22" s="10"/>
+    </x:row>
+    <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A23" s="10"/>
       <x:c r="B23" s="10"/>
       <x:c r="C23" s="10"/>
-      <x:c r="D23" s="10"/>
+      <x:c r="D23" s="9"/>
       <x:c r="E23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F23" s="10"/>
+    </x:row>
+    <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A24" s="10"/>
       <x:c r="B24" s="10"/>
       <x:c r="C24" s="10"/>
-      <x:c r="D24" s="10"/>
+      <x:c r="D24" s="9"/>
       <x:c r="E24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F24" s="10"/>
+    </x:row>
+    <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A25" s="10"/>
       <x:c r="B25" s="10"/>
       <x:c r="C25" s="10"/>
-      <x:c r="D25" s="10"/>
+      <x:c r="D25" s="9"/>
       <x:c r="E25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F25" s="10"/>
+    </x:row>
+    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="11"/>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="11"/>
       <x:c r="D26" s="11"/>
       <x:c r="E26" s="11"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F26" s="11"/>
+    </x:row>
+    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="11"/>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="11"/>
       <x:c r="D27" s="11"/>
       <x:c r="E27" s="11"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F27" s="11"/>
+    </x:row>
+    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="11"/>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="11"/>
       <x:c r="D28" s="11"/>
       <x:c r="E28" s="11"/>
-    </x:row>
-    <x:row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F28" s="11"/>
+    </x:row>
+    <x:row r="29" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A29" s="11"/>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="11"/>
       <x:c r="D29" s="11"/>
       <x:c r="E29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F29" s="11"/>
+    </x:row>
+    <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A30" s="11"/>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="11"/>
       <x:c r="D30" s="11"/>
       <x:c r="E30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F30" s="11"/>
+    </x:row>
+    <x:row r="31" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A31" s="11"/>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="11"/>
       <x:c r="D31" s="11"/>
       <x:c r="E31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F31" s="11"/>
+    </x:row>
+    <x:row r="32" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A32" s="12"/>
       <x:c r="B32" s="12"/>
       <x:c r="C32" s="12"/>
       <x:c r="D32" s="12"/>
       <x:c r="E32" s="12"/>
-    </x:row>
-    <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F32" s="12"/>
+    </x:row>
+    <x:row r="33" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A33" s="12"/>
       <x:c r="B33" s="12"/>
       <x:c r="C33" s="12"/>
       <x:c r="D33" s="12"/>
       <x:c r="E33" s="12"/>
-    </x:row>
-    <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F33" s="12"/>
+    </x:row>
+    <x:row r="34" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A34" s="12"/>
       <x:c r="B34" s="12"/>
       <x:c r="C34" s="12"/>
       <x:c r="D34" s="12"/>
       <x:c r="E34" s="12"/>
-    </x:row>
-    <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F34" s="12"/>
+    </x:row>
+    <x:row r="35" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A35" s="12"/>
       <x:c r="B35" s="12"/>
       <x:c r="C35" s="12"/>
       <x:c r="D35" s="12"/>
       <x:c r="E35" s="12"/>
+      <x:c r="F35" s="12"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
@@ -2251,7 +2295,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -24,18 +24,33 @@
     <x:t>두둥..지금.. 배가 고픕니다!</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 세계에 접속했습니다...&lt;np&gt;이 세계에서 빠져나가고 싶다면&lt;np&gt;몬스터를 물리치세요..</x:t>
+  </x:si>
+  <x:si>
     <x:t>Texture2D/Texture2D_Loading_1</x:t>
   </x:si>
   <x:si>
     <x:t>다만 아직 야근이 남아 있습니다. 좀 더 고생해주세요.</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_group_mainstream_1_2_300</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_group_mainstream_1_2_100</x:t>
   </x:si>
   <x:si>
@@ -45,27 +60,30 @@
     <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
   </x:si>
   <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용사님이시어..고생하셨군요</x:t>
+  </x:si>
+  <x:si>
     <x:t>NextDialogueId</x:t>
   </x:si>
   <x:si>
-    <x:t>용사님이시어..고생하셨군요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_mainstream_1_1_300</x:t>
   </x:si>
   <x:si>
@@ -75,25 +93,7 @@
     <x:t>dialogue_mainstream_1_1_100</x:t>
   </x:si>
   <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 세계에 접속했습니다...&lt;np&gt;이 세계에서 빠져나가고 싶다면&lt;np&gt;몬스터를 물리치세요..</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -862,7 +862,7 @@
   <x:dimension ref="A1:P35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.36328125" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="36.77734375" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="84.22265625" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="32" style="1" customWidth="1"/>
@@ -871,7 +871,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -881,55 +881,55 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="6"/>
       <x:c r="C4" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F4" s="5"/>
       <x:c r="G4" s="4"/>
@@ -945,11 +945,11 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="6"/>
       <x:c r="C5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5"/>
@@ -967,16 +967,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="6"/>
       <x:c r="C6" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
@@ -991,7 +991,7 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="5"/>
       <x:c r="C7" s="5" t="s">
@@ -1013,11 +1013,11 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
@@ -1035,16 +1035,16 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
@@ -1059,11 +1059,11 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="8"/>
       <x:c r="C10" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="8"/>
       <x:c r="E10" s="8"/>
@@ -2295,7 +2295,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -21,76 +21,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>두둥..지금.. 배가 고픕니다!</x:t>
   </x:si>
   <x:si>
+    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다만 아직 야근이 남아 있습니다. 좀 더 고생해주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_100</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>TexturePath</x:t>
   </x:si>
   <x:si>
     <x:t>VoicePath</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 세계에 접속했습니다...&lt;np&gt;이 세계에서 빠져나가고 싶다면&lt;np&gt;몬스터를 물리치세요..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Texture2D_Loading_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다만 아직 야근이 남아 있습니다. 좀 더 고생해주세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
+    <x:t>오늘도 공주는 백성들을 위한 식량을 구하기 위해 길을 나섰다..&lt;np&gt;오늘의 목표는 돼지 사냥!&lt;np&gt;돼지 20마리를 처치하면 미션 성공이다.</x:t>
   </x:si>
   <x:si>
     <x:t>CharacterDataId</x:t>
   </x:si>
   <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
     <x:t>용사님이시어..고생하셨군요</x:t>
   </x:si>
   <x:si>
-    <x:t>NextDialogueId</x:t>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainstream_1_1_300</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
   </x:si>
   <x:si>
     <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
@@ -864,14 +864,14 @@
   <x:cols>
     <x:col min="1" max="1" width="36.77734375" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="84.22265625" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="120.33203125" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="32" style="1" customWidth="1"/>
     <x:col min="5" max="6" width="50.7265625" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -881,51 +881,51 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="6"/>
       <x:c r="C4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5" t="s">
@@ -945,11 +945,11 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="6"/>
       <x:c r="C5" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5"/>
@@ -967,7 +967,7 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="6"/>
       <x:c r="C6" s="5" t="s">
@@ -976,7 +976,7 @@
       <x:c r="D6" s="5"/>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
@@ -991,11 +991,11 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="5"/>
       <x:c r="C7" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D7" s="5"/>
       <x:c r="E7" s="5"/>
@@ -1013,11 +1013,11 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
@@ -1035,16 +1035,16 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
@@ -1059,7 +1059,7 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="8"/>
       <x:c r="C10" s="8" t="s">
